--- a/Proyecto Interno/interno/03_models/coca/coca_results.xlsx
+++ b/Proyecto Interno/interno/03_models/coca/coca_results.xlsx
@@ -1,122 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/interno/03_models/coca/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_248ADFC78F79A8536E3CA493EA7BD2729A480576" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DBBC8FD-B7F8-4037-8A32-240F9ABDB916}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="29">
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>quantity</t>
-  </si>
-  <si>
-    <t>Demo_Group</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>cost_day</t>
-  </si>
-  <si>
-    <t>Cost_1000kcal</t>
-  </si>
-  <si>
-    <t>ciudad</t>
-  </si>
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>mes</t>
-  </si>
-  <si>
-    <t>Maíz blanco trillado</t>
-  </si>
-  <si>
-    <t>[10, 14)</t>
-  </si>
-  <si>
-    <t>BARRANQUILLA</t>
-  </si>
-  <si>
-    <t>[31,51)</t>
-  </si>
-  <si>
-    <t>BOGOTA</t>
-  </si>
-  <si>
-    <t>Maíz blanco cáscara</t>
-  </si>
-  <si>
-    <t>BUCARAMANGA</t>
-  </si>
-  <si>
-    <t>CALI</t>
-  </si>
-  <si>
-    <t>CARTAGENA</t>
-  </si>
-  <si>
-    <t>Harina precocida de maíz</t>
-  </si>
-  <si>
-    <t>CUCUTA</t>
-  </si>
-  <si>
-    <t>Harina de trigo</t>
-  </si>
-  <si>
-    <t>IBAGUE</t>
-  </si>
-  <si>
-    <t>MANIZALES</t>
-  </si>
-  <si>
-    <t>MEDELLIN</t>
-  </si>
-  <si>
-    <t>MONTERIA</t>
-  </si>
-  <si>
-    <t>PASTO</t>
-  </si>
-  <si>
-    <t>PEREIRA</t>
-  </si>
-  <si>
-    <t>VILLAVICENCIO</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,21 +67,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -217,7 +111,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -251,7 +145,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -286,10 +179,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -462,71 +354,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>10</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Demo_Group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cost_day</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cost_1000kcal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ciudad</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B2">
-        <v>615.51128584336527</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
+        <v>615.5112858433653</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1938.8605504066011</v>
+        <v>1938.860550406601</v>
       </c>
       <c r="F2">
-        <v>882.35294117647061</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
+        <v>882.3529411764708</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H2" s="2">
         <v>45839</v>
@@ -538,27 +451,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B3">
-        <v>610.12800782552131</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
+        <v>610.1280078255213</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1921.9032246503921</v>
+        <v>1921.903224650393</v>
       </c>
       <c r="F3">
-        <v>882.35294117647072</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
+        <v>882.3529411764709</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H3" s="2">
         <v>45839</v>
@@ -570,27 +489,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B4">
-        <v>817.07227557310489</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
+        <v>817.0722755731049</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2573.7776680552811</v>
+        <v>2573.777668055281</v>
       </c>
       <c r="F4">
-        <v>882.35294117647084</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
+        <v>882.3529411764709</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H4" s="2">
         <v>45839</v>
@@ -602,27 +527,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B5">
-        <v>615.51128584336527</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
+        <v>615.5112858433654</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1938.8605504066011</v>
+        <v>1938.860550406601</v>
       </c>
       <c r="F5">
-        <v>882.35294117647061</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H5" s="2">
         <v>45870</v>
@@ -634,27 +565,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B6">
-        <v>610.12800782552131</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
+        <v>610.1280078255213</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1921.9032246503921</v>
+        <v>1921.903224650392</v>
       </c>
       <c r="F6">
-        <v>882.35294117647072</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H6" s="2">
         <v>45870</v>
@@ -666,27 +603,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B7">
-        <v>817.07227557310489</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
+        <v>817.0722755731049</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2573.7776680552811</v>
+        <v>2573.777668055281</v>
       </c>
       <c r="F7">
-        <v>882.35294117647084</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
+        <v>882.3529411764708</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H7" s="2">
         <v>45870</v>
@@ -698,27 +641,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B8">
-        <v>615.51128584336527</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
+        <v>615.5112858433653</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>1938.8605504066011</v>
+        <v>1938.860550406601</v>
       </c>
       <c r="F8">
-        <v>882.35294117647061</v>
-      </c>
-      <c r="G8" t="s">
-        <v>12</v>
+        <v>882.3529411764708</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H8" s="2">
         <v>45901</v>
@@ -730,27 +679,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>10</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B9">
-        <v>610.12800782552131</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
+        <v>610.1280078255212</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>1921.9032246503921</v>
+        <v>1921.903224650392</v>
       </c>
       <c r="F9">
-        <v>882.35294117647072</v>
-      </c>
-      <c r="G9" t="s">
-        <v>12</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H9" s="2">
         <v>45901</v>
@@ -762,27 +717,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B10">
-        <v>817.07227557310489</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
+        <v>817.0722755731049</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>2573.7776680552811</v>
+        <v>2573.777668055281</v>
       </c>
       <c r="F10">
-        <v>882.35294117647084</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
+        <v>882.3529411764709</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
       </c>
       <c r="H10" s="2">
         <v>45901</v>
@@ -794,27 +755,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>10</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B11">
-        <v>615.61310694433121</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
+        <v>615.6131069443312</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>1705.2483062357969</v>
+        <v>1705.248306235797</v>
       </c>
       <c r="F11">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H11" s="2">
         <v>45839</v>
@@ -826,27 +793,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>10</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B12">
-        <v>594.79217322031718</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
+        <v>594.7921732203171</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>1647.574319820279</v>
+        <v>1647.574319820278</v>
       </c>
       <c r="F12">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H12" s="2">
         <v>45839</v>
@@ -858,27 +831,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>10</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B13">
-        <v>801.39731569059563</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
+        <v>801.3973156905955</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>2219.8705644629499</v>
+        <v>2219.870564462949</v>
       </c>
       <c r="F13">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H13" s="2">
         <v>45839</v>
@@ -890,27 +869,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>10</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B14">
-        <v>615.61310694433121</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
+        <v>615.6131069443311</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>1705.2483062357969</v>
+        <v>1705.248306235797</v>
       </c>
       <c r="F14">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G14" t="s">
-        <v>14</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H14" s="2">
         <v>45870</v>
@@ -922,27 +907,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>10</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B15">
-        <v>594.79217322031718</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
+        <v>594.792173220317</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>1647.574319820279</v>
+        <v>1647.574319820278</v>
       </c>
       <c r="F15">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G15" t="s">
-        <v>14</v>
+        <v>775.9103641456581</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H15" s="2">
         <v>45870</v>
@@ -954,27 +945,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>10</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B16">
-        <v>801.39731569059563</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
+        <v>801.3973156905955</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>2219.8705644629499</v>
+        <v>2219.870564462949</v>
       </c>
       <c r="F16">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G16" t="s">
-        <v>14</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H16" s="2">
         <v>45870</v>
@@ -986,27 +983,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>15</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B17">
-        <v>605.43768368905296</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
+        <v>605.4376836890528</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1671.0080069817859</v>
+        <v>1671.008006981785</v>
       </c>
       <c r="F17">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G17" t="s">
-        <v>14</v>
+        <v>760.3305785123965</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H17" s="2">
         <v>45901</v>
@@ -1018,15 +1021,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>15</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B18">
-        <v>584.96089762989868</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
+        <v>584.9608976298986</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1035,10 +1042,12 @@
         <v>1614.49207745852</v>
       </c>
       <c r="F18">
-        <v>760.33057851239676</v>
-      </c>
-      <c r="G18" t="s">
-        <v>14</v>
+        <v>760.3305785123964</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H18" s="2">
         <v>45901</v>
@@ -1050,27 +1059,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>15</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B19">
-        <v>788.15107906761057</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
+        <v>788.1510790676103</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>2175.296978226605</v>
+        <v>2175.296978226604</v>
       </c>
       <c r="F19">
-        <v>760.33057851239676</v>
-      </c>
-      <c r="G19" t="s">
-        <v>14</v>
+        <v>760.3305785123964</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOGOTA</t>
+        </is>
       </c>
       <c r="H19" s="2">
         <v>45901</v>
@@ -1082,15 +1097,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>10</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B20">
-        <v>615.17013735092269</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
+        <v>615.1701373509227</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1099,10 +1118,12 @@
         <v>1704.021280462056</v>
       </c>
       <c r="F20">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G20" t="s">
-        <v>16</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H20" s="2">
         <v>45839</v>
@@ -1114,15 +1135,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>10</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B21">
-        <v>596.81164933383411</v>
-      </c>
-      <c r="C21" t="s">
-        <v>13</v>
+        <v>596.8116493338342</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1131,10 +1156,12 @@
         <v>1653.168268654721</v>
       </c>
       <c r="F21">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G21" t="s">
-        <v>16</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H21" s="2">
         <v>45839</v>
@@ -1146,27 +1173,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>10</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B22">
-        <v>804.26830154958134</v>
-      </c>
-      <c r="C22" t="s">
-        <v>13</v>
+        <v>804.2683015495813</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>2227.8231952923411</v>
+        <v>2227.82319529234</v>
       </c>
       <c r="F22">
-        <v>775.91036414565849</v>
-      </c>
-      <c r="G22" t="s">
-        <v>16</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H22" s="2">
         <v>45839</v>
@@ -1178,15 +1211,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>10</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B23">
-        <v>615.17013735092269</v>
-      </c>
-      <c r="C23" t="s">
-        <v>11</v>
+        <v>615.1701373509227</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1195,10 +1232,12 @@
         <v>1704.021280462056</v>
       </c>
       <c r="F23">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G23" t="s">
-        <v>16</v>
+        <v>775.9103641456585</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H23" s="2">
         <v>45870</v>
@@ -1210,15 +1249,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>10</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B24">
-        <v>596.81164933383411</v>
-      </c>
-      <c r="C24" t="s">
-        <v>13</v>
+        <v>596.8116493338341</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1227,10 +1270,12 @@
         <v>1653.168268654721</v>
       </c>
       <c r="F24">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G24" t="s">
-        <v>16</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H24" s="2">
         <v>45870</v>
@@ -1242,27 +1287,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>10</v>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B25">
-        <v>804.26830154958134</v>
-      </c>
-      <c r="C25" t="s">
-        <v>13</v>
+        <v>804.2683015495813</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>2227.8231952923411</v>
+        <v>2227.823195292341</v>
       </c>
       <c r="F25">
-        <v>775.91036414565849</v>
-      </c>
-      <c r="G25" t="s">
-        <v>16</v>
+        <v>775.9103641456585</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H25" s="2">
         <v>45870</v>
@@ -1274,27 +1325,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>15</v>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B26">
-        <v>605.00203590710578</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
+        <v>605.0020359071058</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1669.8056191036119</v>
+        <v>1669.805619103611</v>
       </c>
       <c r="F26">
-        <v>760.33057851239698</v>
-      </c>
-      <c r="G26" t="s">
-        <v>16</v>
+        <v>760.3305785123965</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H26" s="2">
         <v>45901</v>
@@ -1306,27 +1363,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>15</v>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B27">
-        <v>586.94699397294426</v>
-      </c>
-      <c r="C27" t="s">
-        <v>13</v>
+        <v>586.9469939729444</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>1619.9737033653259</v>
+        <v>1619.973703365326</v>
       </c>
       <c r="F27">
-        <v>760.33057851239676</v>
-      </c>
-      <c r="G27" t="s">
-        <v>16</v>
+        <v>760.3305785123966</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H27" s="2">
         <v>45901</v>
@@ -1338,27 +1401,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>15</v>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B28">
-        <v>790.97461061487741</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
+        <v>790.9746106148775</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2183.0899252970621</v>
+        <v>2183.089925297062</v>
       </c>
       <c r="F28">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G28" t="s">
-        <v>16</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>BUCARAMANGA</t>
+        </is>
       </c>
       <c r="H28" s="2">
         <v>45901</v>
@@ -1370,15 +1439,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>10</v>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B29">
-        <v>616.89648769810924</v>
-      </c>
-      <c r="C29" t="s">
-        <v>11</v>
+        <v>616.8964876981092</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1387,10 +1460,12 @@
         <v>1708.803270923763</v>
       </c>
       <c r="F29">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G29" t="s">
-        <v>17</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H29" s="2">
         <v>45839</v>
@@ -1402,15 +1477,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>10</v>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B30">
-        <v>603.93316824463056</v>
-      </c>
-      <c r="C30" t="s">
-        <v>13</v>
+        <v>603.9331682446307</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1419,10 +1498,12 @@
         <v>1672.894876037627</v>
       </c>
       <c r="F30">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G30" t="s">
-        <v>17</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H30" s="2">
         <v>45839</v>
@@ -1434,15 +1515,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>10</v>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B31">
-        <v>815.39762366209277</v>
-      </c>
-      <c r="C31" t="s">
-        <v>13</v>
+        <v>815.3976236620928</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1451,10 +1536,12 @@
         <v>2258.651417543997</v>
       </c>
       <c r="F31">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G31" t="s">
-        <v>17</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H31" s="2">
         <v>45839</v>
@@ -1466,27 +1553,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>10</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B32">
-        <v>616.89648769810924</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
+        <v>616.8964876981092</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>1708.8032709237621</v>
+        <v>1708.803270923763</v>
       </c>
       <c r="F32">
-        <v>775.91036414565804</v>
-      </c>
-      <c r="G32" t="s">
-        <v>17</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H32" s="2">
         <v>45870</v>
@@ -1498,27 +1591,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>10</v>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B33">
-        <v>603.93316824463056</v>
-      </c>
-      <c r="C33" t="s">
-        <v>13</v>
+        <v>603.9331682446307</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>1672.8948760376261</v>
+        <v>1672.894876037627</v>
       </c>
       <c r="F33">
-        <v>775.91036414565815</v>
-      </c>
-      <c r="G33" t="s">
-        <v>17</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H33" s="2">
         <v>45870</v>
@@ -1530,15 +1629,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>10</v>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B34">
-        <v>815.39762366209277</v>
-      </c>
-      <c r="C34" t="s">
-        <v>13</v>
+        <v>815.3976236620928</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1547,10 +1650,12 @@
         <v>2258.651417543997</v>
       </c>
       <c r="F34">
-        <v>775.91036414565815</v>
-      </c>
-      <c r="G34" t="s">
-        <v>17</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H34" s="2">
         <v>45870</v>
@@ -1562,27 +1667,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>15</v>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B35">
-        <v>606.69985153780988</v>
-      </c>
-      <c r="C35" t="s">
-        <v>11</v>
+        <v>606.6998515378099</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>1674.4915902443549</v>
+        <v>1674.491590244355</v>
       </c>
       <c r="F35">
-        <v>760.33057851239664</v>
-      </c>
-      <c r="G35" t="s">
-        <v>17</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H35" s="2">
         <v>45901</v>
@@ -1594,15 +1705,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>15</v>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B36">
-        <v>593.95080182736388</v>
-      </c>
-      <c r="C36" t="s">
-        <v>13</v>
+        <v>593.950801827364</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1611,10 +1726,12 @@
         <v>1639.304213043524</v>
       </c>
       <c r="F36">
-        <v>760.33057851239664</v>
-      </c>
-      <c r="G36" t="s">
-        <v>17</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H36" s="2">
         <v>45901</v>
@@ -1626,27 +1743,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>15</v>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B37">
-        <v>801.91997698999205</v>
-      </c>
-      <c r="C37" t="s">
-        <v>13</v>
+        <v>801.9199769899918</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>2213.2991364923778</v>
+        <v>2213.299136492377</v>
       </c>
       <c r="F37">
-        <v>760.33057851239676</v>
-      </c>
-      <c r="G37" t="s">
-        <v>17</v>
+        <v>760.3305785123965</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>CALI</t>
+        </is>
       </c>
       <c r="H37" s="2">
         <v>45901</v>
@@ -1658,15 +1781,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>10</v>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B38">
-        <v>616.04533336034285</v>
-      </c>
-      <c r="C38" t="s">
-        <v>11</v>
+        <v>616.0453333603429</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1675,10 +1802,12 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F38">
-        <v>882.35294117647061</v>
-      </c>
-      <c r="G38" t="s">
-        <v>18</v>
+        <v>882.3529411764706</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H38" s="2">
         <v>45839</v>
@@ -1690,15 +1819,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>10</v>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B39">
-        <v>611.52903866633756</v>
-      </c>
-      <c r="C39" t="s">
-        <v>13</v>
+        <v>611.5290386663376</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1707,10 +1840,12 @@
         <v>1926.316471798963</v>
       </c>
       <c r="F39">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G39" t="s">
-        <v>18</v>
+        <v>882.3529411764705</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H39" s="2">
         <v>45839</v>
@@ -1722,15 +1857,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>10</v>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B40">
         <v>772.0347671759838</v>
       </c>
-      <c r="C40" t="s">
-        <v>13</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1739,10 +1878,12 @@
         <v>2431.909516604348</v>
       </c>
       <c r="F40">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G40" t="s">
-        <v>18</v>
+        <v>882.3529411764705</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H40" s="2">
         <v>45839</v>
@@ -1754,15 +1895,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>10</v>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B41">
-        <v>616.04533336034285</v>
-      </c>
-      <c r="C41" t="s">
-        <v>11</v>
+        <v>616.0453333603429</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1771,10 +1916,12 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F41">
-        <v>882.35294117647061</v>
-      </c>
-      <c r="G41" t="s">
-        <v>18</v>
+        <v>882.3529411764709</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H41" s="2">
         <v>45870</v>
@@ -1786,15 +1933,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>10</v>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B42">
-        <v>611.52903866633756</v>
-      </c>
-      <c r="C42" t="s">
-        <v>13</v>
+        <v>611.5290386663376</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1803,10 +1954,12 @@
         <v>1926.316471798963</v>
       </c>
       <c r="F42">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G42" t="s">
-        <v>18</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H42" s="2">
         <v>45870</v>
@@ -1818,27 +1971,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>10</v>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B43">
-        <v>772.0347671759838</v>
-      </c>
-      <c r="C43" t="s">
-        <v>13</v>
+        <v>772.0347671759837</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>2431.909516604348</v>
+        <v>2431.909516604349</v>
       </c>
       <c r="F43">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G43" t="s">
-        <v>18</v>
+        <v>882.3529411764708</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H43" s="2">
         <v>45870</v>
@@ -1850,15 +2009,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>10</v>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B44">
-        <v>616.04533336034285</v>
-      </c>
-      <c r="C44" t="s">
-        <v>11</v>
+        <v>616.0453333603429</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1867,10 +2030,12 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F44">
-        <v>882.35294117647061</v>
-      </c>
-      <c r="G44" t="s">
-        <v>18</v>
+        <v>882.3529411764706</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H44" s="2">
         <v>45901</v>
@@ -1882,15 +2047,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>10</v>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B45">
-        <v>611.52903866633756</v>
-      </c>
-      <c r="C45" t="s">
-        <v>13</v>
+        <v>611.5290386663376</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1899,10 +2068,12 @@
         <v>1926.316471798963</v>
       </c>
       <c r="F45">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G45" t="s">
-        <v>18</v>
+        <v>882.3529411764705</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H45" s="2">
         <v>45901</v>
@@ -1914,15 +2085,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>10</v>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B46">
         <v>772.0347671759838</v>
       </c>
-      <c r="C46" t="s">
-        <v>13</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D46">
         <v>0</v>
@@ -1931,10 +2106,12 @@
         <v>2431.909516604348</v>
       </c>
       <c r="F46">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G46" t="s">
-        <v>18</v>
+        <v>882.3529411764705</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CARTAGENA</t>
+        </is>
       </c>
       <c r="H46" s="2">
         <v>45901</v>
@@ -1946,27 +2123,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>19</v>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B47">
-        <v>578.36889633780254</v>
-      </c>
-      <c r="C47" t="s">
-        <v>11</v>
+        <v>610.5005016899029</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47">
-        <v>2058.9932709625759</v>
+        <v>2673.992197401774</v>
       </c>
       <c r="F47">
-        <v>936.84210526315746</v>
-      </c>
-      <c r="G47" t="s">
-        <v>20</v>
+        <v>1216.666666666667</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H47" s="2">
         <v>45839</v>
@@ -1978,27 +2161,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>19</v>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B48">
-        <v>560.68883897941782</v>
-      </c>
-      <c r="C48" t="s">
-        <v>13</v>
+        <v>591.8382189227189</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48">
-        <v>1996.0522667667269</v>
+        <v>2592.251398881509</v>
       </c>
       <c r="F48">
-        <v>936.84210526315758</v>
-      </c>
-      <c r="G48" t="s">
-        <v>20</v>
+        <v>1216.666666666667</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H48" s="2">
         <v>45839</v>
@@ -2010,27 +2199,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>19</v>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B49">
-        <v>755.58890435052763</v>
-      </c>
-      <c r="C49" t="s">
-        <v>13</v>
+        <v>797.5660657033349</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>2689.8964994878779</v>
+        <v>3493.339367780607</v>
       </c>
       <c r="F49">
-        <v>936.84210526315769</v>
-      </c>
-      <c r="G49" t="s">
-        <v>20</v>
+        <v>1216.666666666667</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H49" s="2">
         <v>45839</v>
@@ -2042,27 +2237,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>19</v>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B50">
-        <v>578.36889633780265</v>
-      </c>
-      <c r="C50" t="s">
-        <v>11</v>
+        <v>610.5005016899026</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>2058.9932709625782</v>
+        <v>2576.312117131389</v>
       </c>
       <c r="F50">
-        <v>936.84210526315815</v>
-      </c>
-      <c r="G50" t="s">
-        <v>20</v>
+        <v>1172.222222222222</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H50" s="2">
         <v>45870</v>
@@ -2074,27 +2275,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>19</v>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B51">
-        <v>560.68883897941782</v>
-      </c>
-      <c r="C51" t="s">
-        <v>13</v>
+        <v>591.8382189227189</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51">
-        <v>1996.0522667667281</v>
+        <v>2497.557283853873</v>
       </c>
       <c r="F51">
-        <v>936.84210526315792</v>
-      </c>
-      <c r="G51" t="s">
-        <v>20</v>
+        <v>1172.222222222222</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H51" s="2">
         <v>45870</v>
@@ -2106,27 +2313,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>19</v>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B52">
-        <v>755.58890435052763</v>
-      </c>
-      <c r="C52" t="s">
-        <v>13</v>
+        <v>797.5660657033346</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>2689.8964994878788</v>
+        <v>3365.728797268072</v>
       </c>
       <c r="F52">
-        <v>936.84210526315803</v>
-      </c>
-      <c r="G52" t="s">
-        <v>20</v>
+        <v>1172.222222222222</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H52" s="2">
         <v>45870</v>
@@ -2138,27 +2351,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>21</v>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B53">
-        <v>610.50050168990276</v>
-      </c>
-      <c r="C53" t="s">
-        <v>11</v>
+        <v>610.5005016899025</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="E53">
-        <v>2051.2816856780742</v>
+        <v>2673.992197401773</v>
       </c>
       <c r="F53">
-        <v>933.3333333333336</v>
-      </c>
-      <c r="G53" t="s">
-        <v>20</v>
+        <v>1216.666666666666</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H53" s="2">
         <v>45901</v>
@@ -2170,27 +2389,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>21</v>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B54">
-        <v>591.83821892271885</v>
-      </c>
-      <c r="C54" t="s">
-        <v>13</v>
+        <v>591.8382189227189</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
       <c r="E54">
-        <v>1988.5764155803349</v>
+        <v>2592.251398881509</v>
       </c>
       <c r="F54">
-        <v>933.33333333333337</v>
-      </c>
-      <c r="G54" t="s">
-        <v>20</v>
+        <v>1216.666666666667</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H54" s="2">
         <v>45901</v>
@@ -2202,27 +2427,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>21</v>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Harina de trigo</t>
+        </is>
       </c>
       <c r="B55">
-        <v>797.56606570333474</v>
-      </c>
-      <c r="C55" t="s">
-        <v>13</v>
+        <v>797.5660657033346</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>2679.8219807632049</v>
+        <v>3493.339367780606</v>
       </c>
       <c r="F55">
-        <v>933.33333333333337</v>
-      </c>
-      <c r="G55" t="s">
-        <v>20</v>
+        <v>1216.666666666667</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CUCUTA</t>
+        </is>
       </c>
       <c r="H55" s="2">
         <v>45901</v>
@@ -2234,27 +2465,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>10</v>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B56">
-        <v>616.89381635006941</v>
-      </c>
-      <c r="C56" t="s">
-        <v>11</v>
+        <v>616.8938163500694</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56">
-        <v>1708.7958712896921</v>
+        <v>1708.795871289692</v>
       </c>
       <c r="F56">
-        <v>775.91036414565804</v>
-      </c>
-      <c r="G56" t="s">
-        <v>22</v>
+        <v>775.910364145658</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H56" s="2">
         <v>45839</v>
@@ -2266,15 +2503,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>10</v>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B57">
-        <v>593.57286580882749</v>
-      </c>
-      <c r="C57" t="s">
-        <v>13</v>
+        <v>593.5728658088275</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2283,10 +2524,12 @@
         <v>1644.196838290452</v>
       </c>
       <c r="F57">
-        <v>775.91036414565804</v>
-      </c>
-      <c r="G57" t="s">
-        <v>22</v>
+        <v>775.910364145658</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H57" s="2">
         <v>45839</v>
@@ -2298,27 +2541,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>10</v>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B58">
-        <v>796.46135214408491</v>
-      </c>
-      <c r="C58" t="s">
-        <v>13</v>
+        <v>796.4613521440849</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>2206.1979454391148</v>
+        <v>2206.197945439115</v>
       </c>
       <c r="F58">
-        <v>775.91036414565815</v>
-      </c>
-      <c r="G58" t="s">
-        <v>22</v>
+        <v>775.9103641456581</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H58" s="2">
         <v>45839</v>
@@ -2330,27 +2579,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>10</v>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B59">
-        <v>616.89381635006941</v>
-      </c>
-      <c r="C59" t="s">
-        <v>11</v>
+        <v>616.8938163500695</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59">
-        <v>1708.7958712896921</v>
+        <v>1708.795871289693</v>
       </c>
       <c r="F59">
-        <v>775.91036414565804</v>
-      </c>
-      <c r="G59" t="s">
-        <v>22</v>
+        <v>775.9103641456585</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H59" s="2">
         <v>45870</v>
@@ -2362,27 +2617,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>10</v>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B60">
-        <v>593.57286580882749</v>
-      </c>
-      <c r="C60" t="s">
-        <v>13</v>
+        <v>593.5728658088276</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
       <c r="E60">
-        <v>1644.196838290452</v>
+        <v>1644.196838290453</v>
       </c>
       <c r="F60">
-        <v>775.91036414565804</v>
-      </c>
-      <c r="G60" t="s">
-        <v>22</v>
+        <v>775.9103641456585</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H60" s="2">
         <v>45870</v>
@@ -2394,27 +2655,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>10</v>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B61">
-        <v>796.46135214408491</v>
-      </c>
-      <c r="C61" t="s">
-        <v>13</v>
+        <v>796.4613521440849</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>2206.1979454391148</v>
+        <v>2206.197945439116</v>
       </c>
       <c r="F61">
-        <v>775.91036414565815</v>
-      </c>
-      <c r="G61" t="s">
-        <v>22</v>
+        <v>775.9103641456585</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H61" s="2">
         <v>45870</v>
@@ -2426,15 +2693,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>15</v>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B62">
-        <v>606.69722434428331</v>
-      </c>
-      <c r="C62" t="s">
-        <v>11</v>
+        <v>606.6972243442833</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2443,10 +2714,12 @@
         <v>1674.484339190222</v>
       </c>
       <c r="F62">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G62" t="s">
-        <v>22</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H62" s="2">
         <v>45901</v>
@@ -2458,27 +2731,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>15</v>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B63">
-        <v>583.76174405992128</v>
-      </c>
-      <c r="C63" t="s">
-        <v>13</v>
+        <v>583.7617440599212</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63">
-        <v>1611.1824136053831</v>
+        <v>1611.182413605383</v>
       </c>
       <c r="F63">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G63" t="s">
-        <v>22</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H63" s="2">
         <v>45901</v>
@@ -2490,27 +2769,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>15</v>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B64">
-        <v>783.29670169542248</v>
-      </c>
-      <c r="C64" t="s">
-        <v>13</v>
+        <v>783.2967016954223</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>2161.8988966793659</v>
+        <v>2161.898896679365</v>
       </c>
       <c r="F64">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G64" t="s">
-        <v>22</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>IBAGUE</t>
+        </is>
       </c>
       <c r="H64" s="2">
         <v>45901</v>
@@ -2522,27 +2807,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>15</v>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B65">
-        <v>607.20199734786479</v>
-      </c>
-      <c r="C65" t="s">
-        <v>11</v>
+        <v>607.2019973478648</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>2064.4867909827399</v>
+        <v>2064.48679098274</v>
       </c>
       <c r="F65">
-        <v>936.63911845730036</v>
-      </c>
-      <c r="G65" t="s">
-        <v>23</v>
+        <v>936.6391184573004</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H65" s="2">
         <v>45839</v>
@@ -2554,27 +2845,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>15</v>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B66">
-        <v>582.06729407879584</v>
-      </c>
-      <c r="C66" t="s">
-        <v>13</v>
+        <v>582.0672940787958</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66">
-        <v>1979.0287998679059</v>
+        <v>1979.028799867906</v>
       </c>
       <c r="F66">
-        <v>936.63911845730036</v>
-      </c>
-      <c r="G66" t="s">
-        <v>23</v>
+        <v>936.6391184573004</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H66" s="2">
         <v>45839</v>
@@ -2586,27 +2883,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>15</v>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B67">
-        <v>778.51073838483808</v>
-      </c>
-      <c r="C67" t="s">
-        <v>13</v>
+        <v>778.5107383848381</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>2646.9365105084489</v>
+        <v>2646.936510508449</v>
       </c>
       <c r="F67">
-        <v>936.63911845730036</v>
-      </c>
-      <c r="G67" t="s">
-        <v>23</v>
+        <v>936.6391184573004</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H67" s="2">
         <v>45839</v>
@@ -2618,27 +2921,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>15</v>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B68">
-        <v>607.20199734786479</v>
-      </c>
-      <c r="C68" t="s">
-        <v>11</v>
+        <v>607.2019973478647</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68">
-        <v>2064.4867909827399</v>
+        <v>2064.48679098274</v>
       </c>
       <c r="F68">
-        <v>936.63911845730036</v>
-      </c>
-      <c r="G68" t="s">
-        <v>23</v>
+        <v>936.6391184573001</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H68" s="2">
         <v>45870</v>
@@ -2650,27 +2959,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>15</v>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B69">
-        <v>582.06729407879584</v>
-      </c>
-      <c r="C69" t="s">
-        <v>13</v>
+        <v>582.0672940787958</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1979.0287998679059</v>
+        <v>1979.028799867906</v>
       </c>
       <c r="F69">
-        <v>936.63911845730036</v>
-      </c>
-      <c r="G69" t="s">
-        <v>23</v>
+        <v>936.6391184573002</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H69" s="2">
         <v>45870</v>
@@ -2682,27 +2997,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>15</v>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B70">
-        <v>778.51073838483808</v>
-      </c>
-      <c r="C70" t="s">
-        <v>13</v>
+        <v>778.5107383848381</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>2646.9365105084489</v>
+        <v>2646.936510508449</v>
       </c>
       <c r="F70">
-        <v>936.63911845730036</v>
-      </c>
-      <c r="G70" t="s">
-        <v>23</v>
+        <v>936.6391184573004</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H70" s="2">
         <v>45870</v>
@@ -2714,15 +3035,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>15</v>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B71">
-        <v>607.20199734786479</v>
-      </c>
-      <c r="C71" t="s">
-        <v>11</v>
+        <v>607.2019973478648</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2731,10 +3056,12 @@
         <v>1675.877512680107</v>
       </c>
       <c r="F71">
-        <v>760.33057851239664</v>
-      </c>
-      <c r="G71" t="s">
-        <v>23</v>
+        <v>760.3305785123969</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H71" s="2">
         <v>45901</v>
@@ -2746,27 +3073,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>15</v>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B72">
-        <v>582.06729407879584</v>
-      </c>
-      <c r="C72" t="s">
-        <v>13</v>
+        <v>582.0672940787958</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
       <c r="E72">
-        <v>1606.505731657476</v>
+        <v>1606.505731657477</v>
       </c>
       <c r="F72">
-        <v>760.33057851239676</v>
-      </c>
-      <c r="G72" t="s">
-        <v>23</v>
+        <v>760.3305785123969</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H72" s="2">
         <v>45901</v>
@@ -2778,27 +3111,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>15</v>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B73">
-        <v>778.51073838483808</v>
-      </c>
-      <c r="C73" t="s">
-        <v>13</v>
+        <v>778.510738384838</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>2148.6896379421528</v>
+        <v>2148.689637942153</v>
       </c>
       <c r="F73">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G73" t="s">
-        <v>23</v>
+        <v>760.3305785123969</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MANIZALES</t>
+        </is>
       </c>
       <c r="H73" s="2">
         <v>45901</v>
@@ -2810,27 +3149,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>10</v>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B74">
-        <v>616.48419530413787</v>
-      </c>
-      <c r="C74" t="s">
-        <v>11</v>
+        <v>616.4841953041379</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74">
-        <v>1707.6612209924619</v>
+        <v>1707.661220992462</v>
       </c>
       <c r="F74">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G74" t="s">
-        <v>24</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H74" s="2">
         <v>45839</v>
@@ -2842,27 +3187,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>10</v>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B75">
-        <v>595.48241006017111</v>
-      </c>
-      <c r="C75" t="s">
-        <v>13</v>
+        <v>595.4824100601711</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75">
-        <v>1649.4862758666741</v>
+        <v>1649.486275866674</v>
       </c>
       <c r="F75">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G75" t="s">
-        <v>24</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H75" s="2">
         <v>45839</v>
@@ -2874,15 +3225,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>10</v>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B76">
-        <v>753.64394896656586</v>
-      </c>
-      <c r="C76" t="s">
-        <v>13</v>
+        <v>753.6439489665659</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2891,10 +3246,12 @@
         <v>2087.593738637388</v>
       </c>
       <c r="F76">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G76" t="s">
-        <v>24</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H76" s="2">
         <v>45839</v>
@@ -2906,27 +3263,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>10</v>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B77">
-        <v>616.48419530413798</v>
-      </c>
-      <c r="C77" t="s">
-        <v>11</v>
+        <v>616.4841953041379</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D77">
         <v>1</v>
       </c>
       <c r="E77">
-        <v>1707.6612209924619</v>
+        <v>1707.661220992462</v>
       </c>
       <c r="F77">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G77" t="s">
-        <v>24</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H77" s="2">
         <v>45870</v>
@@ -2938,15 +3301,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>10</v>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B78">
-        <v>595.48241006017133</v>
-      </c>
-      <c r="C78" t="s">
-        <v>13</v>
+        <v>595.4824100601713</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D78">
         <v>1</v>
@@ -2955,10 +3322,12 @@
         <v>1649.486275866675</v>
       </c>
       <c r="F78">
-        <v>775.91036414565849</v>
-      </c>
-      <c r="G78" t="s">
-        <v>24</v>
+        <v>775.9103641456585</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H78" s="2">
         <v>45870</v>
@@ -2970,15 +3339,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>10</v>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B79">
-        <v>753.64394896656586</v>
-      </c>
-      <c r="C79" t="s">
-        <v>13</v>
+        <v>753.6439489665659</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2987,10 +3360,12 @@
         <v>2087.593738637388</v>
       </c>
       <c r="F79">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G79" t="s">
-        <v>24</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H79" s="2">
         <v>45870</v>
@@ -3002,15 +3377,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>15</v>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B80">
-        <v>606.29437389415216</v>
-      </c>
-      <c r="C80" t="s">
-        <v>11</v>
+        <v>606.2943738941522</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3019,10 +3398,12 @@
         <v>1673.37247194786</v>
       </c>
       <c r="F80">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G80" t="s">
-        <v>24</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H80" s="2">
         <v>45901</v>
@@ -3034,15 +3415,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>15</v>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B81">
         <v>585.6397255963667</v>
       </c>
-      <c r="C81" t="s">
-        <v>13</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3051,10 +3436,12 @@
         <v>1616.365642645972</v>
       </c>
       <c r="F81">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G81" t="s">
-        <v>24</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H81" s="2">
         <v>45901</v>
@@ -3066,27 +3453,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>15</v>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B82">
-        <v>741.18702419025897</v>
-      </c>
-      <c r="C82" t="s">
-        <v>13</v>
+        <v>741.1870241902589</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82">
-        <v>2045.6761867651151</v>
+        <v>2045.676186765115</v>
       </c>
       <c r="F82">
-        <v>760.33057851239698</v>
-      </c>
-      <c r="G82" t="s">
-        <v>24</v>
+        <v>760.3305785123966</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>MEDELLIN</t>
+        </is>
       </c>
       <c r="H82" s="2">
         <v>45901</v>
@@ -3098,27 +3491,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>10</v>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B83">
-        <v>615.24240320708543</v>
-      </c>
-      <c r="C83" t="s">
-        <v>11</v>
+        <v>615.2424032070855</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>1938.0135701023189</v>
+        <v>1938.013570102319</v>
       </c>
       <c r="F83">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G83" t="s">
-        <v>25</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H83" s="2">
         <v>45839</v>
@@ -3130,27 +3529,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>10</v>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B84">
-        <v>640.87971373036726</v>
-      </c>
-      <c r="C84" t="s">
-        <v>13</v>
+        <v>640.8797137303674</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>2018.771098250656</v>
+        <v>2018.771098250657</v>
       </c>
       <c r="F84">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G84" t="s">
-        <v>25</v>
+        <v>882.3529411764708</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H84" s="2">
         <v>45839</v>
@@ -3162,27 +3567,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>10</v>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B85">
-        <v>801.16959755064534</v>
-      </c>
-      <c r="C85" t="s">
-        <v>13</v>
+        <v>801.1695975506458</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>2523.6842322845318</v>
+        <v>2523.684232284534</v>
       </c>
       <c r="F85">
-        <v>882.35294117647015</v>
-      </c>
-      <c r="G85" t="s">
-        <v>25</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H85" s="2">
         <v>45839</v>
@@ -3194,27 +3605,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>19</v>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B86">
-        <v>578.00404722349879</v>
-      </c>
-      <c r="C86" t="s">
-        <v>11</v>
+        <v>615.2424032070853</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>1895.8532748930761</v>
+        <v>1938.013570102319</v>
       </c>
       <c r="F86">
-        <v>863.1578947368422</v>
-      </c>
-      <c r="G86" t="s">
-        <v>25</v>
+        <v>882.3529411764706</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H86" s="2">
         <v>45870</v>
@@ -3226,27 +3643,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>19</v>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B87">
-        <v>602.08962579405568</v>
-      </c>
-      <c r="C87" t="s">
-        <v>13</v>
+        <v>640.8797137303673</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>1974.853972604503</v>
+        <v>2018.771098250657</v>
       </c>
       <c r="F87">
-        <v>863.1578947368422</v>
-      </c>
-      <c r="G87" t="s">
-        <v>25</v>
+        <v>882.3529411764706</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H87" s="2">
         <v>45870</v>
@@ -3258,27 +3681,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>19</v>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B88">
-        <v>752.67775348836983</v>
-      </c>
-      <c r="C88" t="s">
-        <v>13</v>
+        <v>801.1695975506456</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>2468.7830314418529</v>
+        <v>2523.684232284534</v>
       </c>
       <c r="F88">
-        <v>863.1578947368422</v>
-      </c>
-      <c r="G88" t="s">
-        <v>25</v>
+        <v>882.3529411764706</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H88" s="2">
         <v>45870</v>
@@ -3290,27 +3719,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>10</v>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B89">
-        <v>615.24240320708543</v>
-      </c>
-      <c r="C89" t="s">
-        <v>11</v>
+        <v>615.2424032070855</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>1938.0135701023189</v>
+        <v>1938.013570102319</v>
       </c>
       <c r="F89">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G89" t="s">
-        <v>25</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H89" s="2">
         <v>45901</v>
@@ -3322,27 +3757,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>10</v>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B90">
-        <v>640.87971373036726</v>
-      </c>
-      <c r="C90" t="s">
-        <v>13</v>
+        <v>640.8797137303674</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90">
-        <v>2018.771098250656</v>
+        <v>2018.771098250657</v>
       </c>
       <c r="F90">
-        <v>882.35294117647049</v>
-      </c>
-      <c r="G90" t="s">
-        <v>25</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H90" s="2">
         <v>45901</v>
@@ -3354,27 +3795,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>10</v>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B91">
-        <v>801.16959755064534</v>
-      </c>
-      <c r="C91" t="s">
-        <v>13</v>
+        <v>801.1695975506458</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>2523.6842322845318</v>
+        <v>2523.684232284534</v>
       </c>
       <c r="F91">
-        <v>882.35294117647015</v>
-      </c>
-      <c r="G91" t="s">
-        <v>25</v>
+        <v>882.3529411764707</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>MONTERIA</t>
+        </is>
       </c>
       <c r="H91" s="2">
         <v>45901</v>
@@ -3386,15 +3833,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>10</v>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B92">
-        <v>617.41414245336671</v>
-      </c>
-      <c r="C92" t="s">
-        <v>11</v>
+        <v>617.4141424533667</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3403,10 +3854,12 @@
         <v>1710.237174595826</v>
       </c>
       <c r="F92">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G92" t="s">
-        <v>26</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H92" s="2">
         <v>45839</v>
@@ -3418,27 +3871,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>10</v>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B93">
-        <v>582.53748114568339</v>
-      </c>
-      <c r="C93" t="s">
-        <v>13</v>
+        <v>582.5374811456834</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93">
-        <v>1613.6288227735431</v>
+        <v>1613.628822773543</v>
       </c>
       <c r="F93">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G93" t="s">
-        <v>26</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H93" s="2">
         <v>45839</v>
@@ -3450,27 +3909,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>10</v>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B94">
-        <v>774.42263004746872</v>
-      </c>
-      <c r="C94" t="s">
-        <v>13</v>
+        <v>774.4226300474687</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
       <c r="E94">
-        <v>2145.1506852314878</v>
+        <v>2145.150685231488</v>
       </c>
       <c r="F94">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G94" t="s">
-        <v>26</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H94" s="2">
         <v>45839</v>
@@ -3482,15 +3947,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>10</v>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B95">
-        <v>617.41414245336671</v>
-      </c>
-      <c r="C95" t="s">
-        <v>11</v>
+        <v>617.4141424533667</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3499,10 +3968,12 @@
         <v>1710.237174595826</v>
       </c>
       <c r="F95">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G95" t="s">
-        <v>26</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H95" s="2">
         <v>45870</v>
@@ -3514,27 +3985,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>10</v>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B96">
-        <v>582.53748114568339</v>
-      </c>
-      <c r="C96" t="s">
-        <v>13</v>
+        <v>582.5374811456834</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>1613.6288227735431</v>
+        <v>1613.628822773543</v>
       </c>
       <c r="F96">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G96" t="s">
-        <v>26</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H96" s="2">
         <v>45870</v>
@@ -3546,27 +4023,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>10</v>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B97">
-        <v>774.42263004746872</v>
-      </c>
-      <c r="C97" t="s">
-        <v>13</v>
+        <v>774.4226300474687</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>2145.1506852314878</v>
+        <v>2145.150685231488</v>
       </c>
       <c r="F97">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G97" t="s">
-        <v>26</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H97" s="2">
         <v>45870</v>
@@ -3578,27 +4061,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>15</v>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B98">
-        <v>607.20895001612098</v>
-      </c>
-      <c r="C98" t="s">
-        <v>11</v>
+        <v>607.208950016121</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>1675.8967020444941</v>
+        <v>1675.896702044494</v>
       </c>
       <c r="F98">
-        <v>760.33057851239698</v>
-      </c>
-      <c r="G98" t="s">
-        <v>26</v>
+        <v>760.330578512397</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H98" s="2">
         <v>45901</v>
@@ -3610,15 +4099,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>15</v>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B99">
-        <v>572.90876244906065</v>
-      </c>
-      <c r="C99" t="s">
-        <v>13</v>
+        <v>572.9087624490606</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3629,8 +4122,10 @@
       <c r="F99">
         <v>760.3305785123971</v>
       </c>
-      <c r="G99" t="s">
-        <v>26</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H99" s="2">
         <v>45901</v>
@@ -3642,15 +4137,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>15</v>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B100">
-        <v>761.62225599709734</v>
-      </c>
-      <c r="C100" t="s">
-        <v>13</v>
+        <v>761.6222559970973</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3659,10 +4158,12 @@
         <v>2102.077426551989</v>
       </c>
       <c r="F100">
-        <v>760.33057851239698</v>
-      </c>
-      <c r="G100" t="s">
-        <v>26</v>
+        <v>760.330578512397</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PASTO</t>
+        </is>
       </c>
       <c r="H100" s="2">
         <v>45901</v>
@@ -3674,15 +4175,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>10</v>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B101">
-        <v>615.75840961678523</v>
-      </c>
-      <c r="C101" t="s">
-        <v>11</v>
+        <v>615.7584096167852</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3691,10 +4196,12 @@
         <v>1705.650794638495</v>
       </c>
       <c r="F101">
-        <v>775.91036414565849</v>
-      </c>
-      <c r="G101" t="s">
-        <v>27</v>
+        <v>775.9103641456585</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H101" s="2">
         <v>45839</v>
@@ -3706,27 +4213,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>10</v>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B102">
-        <v>591.84993767675871</v>
-      </c>
-      <c r="C102" t="s">
-        <v>13</v>
+        <v>591.8499376767587</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>1639.4243273646221</v>
+        <v>1639.424327364622</v>
       </c>
       <c r="F102">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G102" t="s">
-        <v>27</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H102" s="2">
         <v>45839</v>
@@ -3738,27 +4251,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>10</v>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B103">
-        <v>791.59495247533948</v>
-      </c>
-      <c r="C103" t="s">
-        <v>13</v>
+        <v>791.5949524753395</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>2192.7180183566911</v>
+        <v>2192.718018356691</v>
       </c>
       <c r="F103">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G103" t="s">
-        <v>27</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H103" s="2">
         <v>45839</v>
@@ -3770,15 +4289,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>10</v>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B104">
-        <v>615.75840961678523</v>
-      </c>
-      <c r="C104" t="s">
-        <v>11</v>
+        <v>615.7584096167852</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3787,10 +4310,12 @@
         <v>1705.650794638495</v>
       </c>
       <c r="F104">
-        <v>775.91036414565849</v>
-      </c>
-      <c r="G104" t="s">
-        <v>27</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H104" s="2">
         <v>45870</v>
@@ -3802,27 +4327,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>10</v>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B105">
-        <v>591.84993767675871</v>
-      </c>
-      <c r="C105" t="s">
-        <v>13</v>
+        <v>591.8499376767587</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>1639.4243273646221</v>
+        <v>1639.424327364622</v>
       </c>
       <c r="F105">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G105" t="s">
-        <v>27</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H105" s="2">
         <v>45870</v>
@@ -3834,27 +4365,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>10</v>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B106">
-        <v>791.59495247533948</v>
-      </c>
-      <c r="C106" t="s">
-        <v>13</v>
+        <v>791.5949524753396</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>2192.7180183566911</v>
+        <v>2192.718018356691</v>
       </c>
       <c r="F106">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G106" t="s">
-        <v>27</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H106" s="2">
         <v>45870</v>
@@ -3866,15 +4403,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>15</v>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B107">
-        <v>605.58058466444174</v>
-      </c>
-      <c r="C107" t="s">
-        <v>11</v>
+        <v>605.5805846644417</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3883,10 +4424,12 @@
         <v>1671.402413673859</v>
       </c>
       <c r="F107">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G107" t="s">
-        <v>27</v>
+        <v>760.330578512397</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H107" s="2">
         <v>45901</v>
@@ -3898,27 +4441,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>15</v>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B108">
-        <v>582.06729407879584</v>
-      </c>
-      <c r="C108" t="s">
-        <v>13</v>
+        <v>582.0672940787958</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>1606.5057316574771</v>
+        <v>1606.505731657477</v>
       </c>
       <c r="F108">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G108" t="s">
-        <v>27</v>
+        <v>760.3305785123969</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H108" s="2">
         <v>45901</v>
@@ -3930,27 +4479,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>15</v>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B109">
-        <v>778.51073838483808</v>
-      </c>
-      <c r="C109" t="s">
-        <v>13</v>
+        <v>778.5107383848381</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>2148.6896379421528</v>
+        <v>2148.689637942154</v>
       </c>
       <c r="F109">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G109" t="s">
-        <v>27</v>
+        <v>760.330578512397</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>PEREIRA</t>
+        </is>
       </c>
       <c r="H109" s="2">
         <v>45901</v>
@@ -3962,27 +4517,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>10</v>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B110">
-        <v>615.99680813221516</v>
-      </c>
-      <c r="C110" t="s">
-        <v>11</v>
+        <v>615.9968081322152</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>1706.3111585262361</v>
+        <v>1706.311158526236</v>
       </c>
       <c r="F110">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G110" t="s">
-        <v>28</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H110" s="2">
         <v>45839</v>
@@ -3994,27 +4555,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>10</v>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B111">
-        <v>593.46959501795413</v>
-      </c>
-      <c r="C111" t="s">
-        <v>13</v>
+        <v>593.4695950179541</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>1643.9107781997329</v>
+        <v>1643.910778199733</v>
       </c>
       <c r="F111">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G111" t="s">
-        <v>28</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H111" s="2">
         <v>45839</v>
@@ -4026,27 +4593,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>10</v>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B112">
-        <v>795.99376781557783</v>
-      </c>
-      <c r="C112" t="s">
-        <v>13</v>
+        <v>795.9937678155778</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>2204.9027368491511</v>
+        <v>2204.902736849151</v>
       </c>
       <c r="F112">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G112" t="s">
-        <v>28</v>
+        <v>775.9103641456583</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H112" s="2">
         <v>45839</v>
@@ -4058,27 +4631,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>10</v>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B113">
-        <v>615.99680813221516</v>
-      </c>
-      <c r="C113" t="s">
-        <v>11</v>
+        <v>615.9968081322153</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>1706.3111585262361</v>
+        <v>1706.311158526236</v>
       </c>
       <c r="F113">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G113" t="s">
-        <v>28</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H113" s="2">
         <v>45870</v>
@@ -4090,27 +4669,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>10</v>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B114">
-        <v>593.46959501795413</v>
-      </c>
-      <c r="C114" t="s">
-        <v>13</v>
+        <v>593.4695950179541</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>1643.9107781997329</v>
+        <v>1643.910778199733</v>
       </c>
       <c r="F114">
-        <v>775.91036414565838</v>
-      </c>
-      <c r="G114" t="s">
-        <v>28</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H114" s="2">
         <v>45870</v>
@@ -4122,27 +4707,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>10</v>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Maíz blanco trillado</t>
+        </is>
       </c>
       <c r="B115">
-        <v>795.99376781557783</v>
-      </c>
-      <c r="C115" t="s">
-        <v>13</v>
+        <v>795.9937678155779</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>2204.9027368491511</v>
+        <v>2204.902736849151</v>
       </c>
       <c r="F115">
-        <v>775.91036414565826</v>
-      </c>
-      <c r="G115" t="s">
-        <v>28</v>
+        <v>775.9103641456584</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H115" s="2">
         <v>45870</v>
@@ -4154,27 +4745,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>15</v>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B116">
-        <v>605.81504270854225</v>
-      </c>
-      <c r="C116" t="s">
-        <v>11</v>
+        <v>605.8150427085423</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>[10, 14)</t>
+        </is>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116">
-        <v>1672.0495178755771</v>
+        <v>1672.049517875577</v>
       </c>
       <c r="F116">
-        <v>760.33057851239698</v>
-      </c>
-      <c r="G116" t="s">
-        <v>28</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H116" s="2">
         <v>45901</v>
@@ -4186,27 +4783,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>15</v>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B117">
-        <v>583.66018022426886</v>
-      </c>
-      <c r="C117" t="s">
-        <v>13</v>
+        <v>583.6601802242689</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D117">
         <v>1</v>
       </c>
       <c r="E117">
-        <v>1610.902097418983</v>
+        <v>1610.902097418982</v>
       </c>
       <c r="F117">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G117" t="s">
-        <v>28</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H117" s="2">
         <v>45901</v>
@@ -4218,27 +4821,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>15</v>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Maíz blanco cáscara</t>
+        </is>
       </c>
       <c r="B118">
-        <v>782.83684603350218</v>
-      </c>
-      <c r="C118" t="s">
-        <v>13</v>
+        <v>782.8368460335023</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>[31,51)</t>
+        </is>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>2160.629695052467</v>
+        <v>2160.629695052466</v>
       </c>
       <c r="F118">
-        <v>760.33057851239687</v>
-      </c>
-      <c r="G118" t="s">
-        <v>28</v>
+        <v>760.3305785123968</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>VILLAVICENCIO</t>
+        </is>
       </c>
       <c r="H118" s="2">
         <v>45901</v>

--- a/Proyecto Interno/interno/03_models/coca/coca_results.xlsx
+++ b/Proyecto Interno/interno/03_models/coca/coca_results.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>615.5112858433654</v>
+        <v>615.5112858433653</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
         <v>1938.860550406601</v>
       </c>
       <c r="F5">
-        <v>882.3529411764707</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>610.1280078255213</v>
+        <v>610.1280078255212</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>1921.903224650392</v>
       </c>
       <c r="F6">
-        <v>882.3529411764707</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>1938.860550406601</v>
       </c>
       <c r="F8">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>1921.903224650392</v>
       </c>
       <c r="F9">
-        <v>882.3529411764707</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>817.0722755731049</v>
+        <v>817.0722755731047</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -735,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>2573.777668055281</v>
+        <v>2573.77766805528</v>
       </c>
       <c r="F10">
-        <v>882.3529411764709</v>
+        <v>882.3529411764705</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>615.6131069443311</v>
+        <v>615.6131069443312</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>1705.248306235797</v>
       </c>
       <c r="F14">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>594.792173220317</v>
+        <v>594.7921732203171</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>1647.574319820278</v>
       </c>
       <c r="F15">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>605.4376836890528</v>
+        <v>605.437683689053</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1671.008006981785</v>
+        <v>1671.008006981786</v>
       </c>
       <c r="F17">
-        <v>760.3305785123965</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>584.9608976298986</v>
+        <v>584.9608976298987</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>1614.49207745852</v>
       </c>
       <c r="F18">
-        <v>760.3305785123964</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>788.1510790676103</v>
+        <v>788.1510790676106</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>2175.296978226604</v>
+        <v>2175.296978226605</v>
       </c>
       <c r="F19">
-        <v>760.3305785123964</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>1704.021280462056</v>
       </c>
       <c r="F23">
-        <v>775.9103641456585</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>596.8116493338341</v>
+        <v>596.8116493338342</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>2227.823195292341</v>
+        <v>2227.82319529234</v>
       </c>
       <c r="F25">
-        <v>775.9103641456585</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1669.805619103611</v>
+        <v>1669.805619103612</v>
       </c>
       <c r="F26">
-        <v>760.3305785123965</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>1619.973703365326</v>
       </c>
       <c r="F27">
-        <v>760.3305785123966</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>2183.089925297062</v>
       </c>
       <c r="F28">
-        <v>760.3305785123968</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>1708.803270923763</v>
       </c>
       <c r="F32">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>603.9331682446307</v>
+        <v>603.9331682446306</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>1672.894876037627</v>
       </c>
       <c r="F33">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>616.0453333603429</v>
+        <v>616.0453333603427</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F38">
-        <v>882.3529411764706</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>1926.316471798963</v>
       </c>
       <c r="F39">
-        <v>882.3529411764705</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>2431.909516604348</v>
+        <v>2431.909516604349</v>
       </c>
       <c r="F40">
-        <v>882.3529411764705</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>616.0453333603429</v>
+        <v>616.0453333603427</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F41">
-        <v>882.3529411764709</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>772.0347671759837</v>
+        <v>772.0347671759838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>616.0453333603429</v>
+        <v>616.0453333603427</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F44">
-        <v>882.3529411764706</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>1926.316471798963</v>
       </c>
       <c r="F45">
-        <v>882.3529411764705</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>2431.909516604348</v>
+        <v>2431.909516604349</v>
       </c>
       <c r="F46">
-        <v>882.3529411764705</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B47">
-        <v>610.5005016899029</v>
+        <v>622.6067439330452</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2141,10 +2141,10 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>2673.992197401774</v>
+        <v>2042.150120100388</v>
       </c>
       <c r="F47">
-        <v>1216.666666666667</v>
+        <v>929.1784702549575</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2164,11 +2164,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B48">
-        <v>591.8382189227189</v>
+        <v>603.5743875699116</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2179,10 +2179,10 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>2592.251398881509</v>
+        <v>1979.72399122931</v>
       </c>
       <c r="F48">
-        <v>1216.666666666667</v>
+        <v>929.1784702549575</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2202,11 +2202,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B49">
-        <v>797.5660657033349</v>
+        <v>813.3818233801713</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2217,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>3493.339367780607</v>
+        <v>2667.892380686962</v>
       </c>
       <c r="F49">
-        <v>1216.666666666667</v>
+        <v>929.1784702549575</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2240,11 +2240,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B50">
-        <v>610.5005016899026</v>
+        <v>622.6067439330452</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>1</v>
       </c>
       <c r="E50">
-        <v>2576.312117131389</v>
+        <v>2042.150120100389</v>
       </c>
       <c r="F50">
-        <v>1172.222222222222</v>
+        <v>929.1784702549576</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2278,11 +2278,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B51">
-        <v>591.8382189227189</v>
+        <v>603.5743875699116</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="E51">
-        <v>2497.557283853873</v>
+        <v>1979.72399122931</v>
       </c>
       <c r="F51">
-        <v>1172.222222222222</v>
+        <v>929.1784702549577</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2316,11 +2316,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B52">
-        <v>797.5660657033346</v>
+        <v>813.3818233801713</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>3365.728797268072</v>
+        <v>2667.892380686962</v>
       </c>
       <c r="F52">
-        <v>1172.222222222222</v>
+        <v>929.1784702549576</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2354,11 +2354,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B53">
-        <v>610.5005016899025</v>
+        <v>622.6067439330452</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>2673.992197401773</v>
+        <v>2042.150120100389</v>
       </c>
       <c r="F53">
-        <v>1216.666666666666</v>
+        <v>929.1784702549576</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2392,11 +2392,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B54">
-        <v>591.8382189227189</v>
+        <v>603.5743875699116</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>1</v>
       </c>
       <c r="E54">
-        <v>2592.251398881509</v>
+        <v>1979.72399122931</v>
       </c>
       <c r="F54">
-        <v>1216.666666666667</v>
+        <v>929.1784702549577</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2430,11 +2430,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Harina de trigo</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B55">
-        <v>797.5660657033346</v>
+        <v>813.3818233801713</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>3493.339367780606</v>
+        <v>2667.892380686962</v>
       </c>
       <c r="F55">
-        <v>1216.666666666667</v>
+        <v>929.1784702549576</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="B56">
-        <v>616.8938163500694</v>
+        <v>616.8938163500695</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2483,10 +2483,10 @@
         <v>1</v>
       </c>
       <c r="E56">
-        <v>1708.795871289692</v>
+        <v>1708.795871289693</v>
       </c>
       <c r="F56">
-        <v>775.910364145658</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>593.5728658088275</v>
+        <v>593.5728658088276</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>1644.196838290452</v>
       </c>
       <c r="F57">
-        <v>775.910364145658</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>2206.197945439115</v>
       </c>
       <c r="F58">
-        <v>775.9103641456581</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>616.8938163500695</v>
+        <v>616.8938163500694</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>1708.795871289693</v>
+        <v>1708.795871289692</v>
       </c>
       <c r="F59">
-        <v>775.9103641456585</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="E60">
-        <v>1644.196838290453</v>
+        <v>1644.196838290452</v>
       </c>
       <c r="F60">
-        <v>775.9103641456585</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>2206.197945439116</v>
+        <v>2206.197945439115</v>
       </c>
       <c r="F61">
-        <v>775.9103641456585</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>1674.484339190222</v>
       </c>
       <c r="F62">
-        <v>760.3305785123968</v>
+        <v>760.330578512397</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>583.7617440599212</v>
+        <v>583.7617440599213</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>1611.182413605383</v>
       </c>
       <c r="F63">
-        <v>760.3305785123968</v>
+        <v>760.330578512397</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>2161.898896679365</v>
+        <v>2161.898896679366</v>
       </c>
       <c r="F64">
-        <v>760.3305785123968</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2810,11 +2810,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Maíz blanco cáscara</t>
+          <t>Harina precocida de maíz</t>
         </is>
       </c>
       <c r="B65">
-        <v>607.2019973478648</v>
+        <v>580.0376974665129</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="E65">
-        <v>2064.48679098274</v>
+        <v>1711.111207526213</v>
       </c>
       <c r="F65">
-        <v>936.6391184573004</v>
+        <v>776.3157894736839</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2848,11 +2848,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Maíz blanco cáscara</t>
+          <t>Harina precocida de maíz</t>
         </is>
       </c>
       <c r="B66">
-        <v>582.0672940787958</v>
+        <v>556.027441448955</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <v>1979.028799867906</v>
+        <v>1640.280952274417</v>
       </c>
       <c r="F66">
-        <v>936.6391184573004</v>
+        <v>776.315789473684</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2886,11 +2886,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Maíz blanco cáscara</t>
+          <t>Harina precocida de maíz</t>
         </is>
       </c>
       <c r="B67">
-        <v>778.5107383848381</v>
+        <v>743.6826264044637</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>2646.936510508449</v>
+        <v>2193.863747893167</v>
       </c>
       <c r="F67">
-        <v>936.6391184573004</v>
+        <v>776.3157894736839</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2924,11 +2924,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Maíz blanco cáscara</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B68">
-        <v>607.2019973478647</v>
+        <v>624.4031870744332</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
         <v>1</v>
       </c>
       <c r="E68">
-        <v>2064.48679098274</v>
+        <v>2048.042453604141</v>
       </c>
       <c r="F68">
-        <v>936.6391184573001</v>
+        <v>929.1784702549573</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2962,11 +2962,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maíz blanco cáscara</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B69">
-        <v>582.0672940787958</v>
+        <v>598.556452551283</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1979.028799867906</v>
+        <v>1963.265164368208</v>
       </c>
       <c r="F69">
-        <v>936.6391184573002</v>
+        <v>929.1784702549575</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3000,11 +3000,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Maíz blanco cáscara</t>
+          <t>Arroz de segunda</t>
         </is>
       </c>
       <c r="B70">
-        <v>778.5107383848381</v>
+        <v>800.5648669509807</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>2646.936510508449</v>
+        <v>2625.852763599216</v>
       </c>
       <c r="F70">
-        <v>936.6391184573004</v>
+        <v>929.1784702549573</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B71">
-        <v>607.2019973478648</v>
+        <v>607.2019973478647</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>1675.877512680107</v>
       </c>
       <c r="F71">
-        <v>760.3305785123969</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>1606.505731657477</v>
+        <v>1606.505731657476</v>
       </c>
       <c r="F72">
-        <v>760.3305785123969</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B73">
-        <v>778.510738384838</v>
+        <v>778.5107383848381</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>1707.661220992462</v>
       </c>
       <c r="F74">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="B75">
-        <v>595.4824100601711</v>
+        <v>595.4824100601712</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>1649.486275866674</v>
       </c>
       <c r="F75">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>595.4824100601713</v>
+        <v>595.4824100601712</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>1649.486275866675</v>
+        <v>1649.486275866674</v>
       </c>
       <c r="F78">
-        <v>775.9103641456585</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>753.6439489665659</v>
+        <v>753.643948966566</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <v>1673.37247194786</v>
+        <v>1673.372471947861</v>
       </c>
       <c r="F80">
-        <v>760.3305785123968</v>
+        <v>760.3305785123971</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>1616.365642645972</v>
       </c>
       <c r="F81">
-        <v>760.3305785123968</v>
+        <v>760.330578512397</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="B82">
-        <v>741.1870241902589</v>
+        <v>741.187024190259</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>2045.676186765115</v>
       </c>
       <c r="F82">
-        <v>760.3305785123966</v>
+        <v>760.330578512397</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B83">
-        <v>615.2424032070855</v>
+        <v>615.2424032070854</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>1938.013570102319</v>
       </c>
       <c r="F83">
-        <v>882.3529411764707</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="B84">
-        <v>640.8797137303674</v>
+        <v>640.8797137303673</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>2018.771098250657</v>
       </c>
       <c r="F84">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3608,11 +3608,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Maíz blanco trillado</t>
+          <t>Harina precocida de maíz</t>
         </is>
       </c>
       <c r="B86">
-        <v>615.2424032070853</v>
+        <v>578.0040472234987</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
         <v>1</v>
       </c>
       <c r="E86">
-        <v>1938.013570102319</v>
+        <v>1895.853274893075</v>
       </c>
       <c r="F86">
-        <v>882.3529411764706</v>
+        <v>863.157894736842</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3646,11 +3646,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Maíz blanco trillado</t>
+          <t>Harina precocida de maíz</t>
         </is>
       </c>
       <c r="B87">
-        <v>640.8797137303673</v>
+        <v>602.0896257940556</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
         <v>1</v>
       </c>
       <c r="E87">
-        <v>2018.771098250657</v>
+        <v>1974.853972604502</v>
       </c>
       <c r="F87">
-        <v>882.3529411764706</v>
+        <v>863.157894736842</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3684,11 +3684,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Maíz blanco trillado</t>
+          <t>Harina precocida de maíz</t>
         </is>
       </c>
       <c r="B88">
-        <v>801.1695975506456</v>
+        <v>752.6777534883697</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3699,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>2523.684232284534</v>
+        <v>2468.783031441852</v>
       </c>
       <c r="F88">
-        <v>882.3529411764706</v>
+        <v>863.157894736842</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="B89">
-        <v>615.2424032070855</v>
+        <v>615.2424032070854</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="B90">
-        <v>640.8797137303674</v>
+        <v>640.8797137303673</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>2523.684232284534</v>
+        <v>2523.684232284535</v>
       </c>
       <c r="F91">
-        <v>882.3529411764707</v>
+        <v>882.3529411764709</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>1710.237174595826</v>
       </c>
       <c r="F92">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="B94">
-        <v>774.4226300474687</v>
+        <v>774.4226300474685</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>2145.150685231488</v>
       </c>
       <c r="F94">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1710.237174595826</v>
       </c>
       <c r="F95">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="B97">
-        <v>774.4226300474687</v>
+        <v>774.4226300474685</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>2145.150685231488</v>
       </c>
       <c r="F97">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>1675.896702044494</v>
       </c>
       <c r="F98">
-        <v>760.330578512397</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4117,10 +4117,10 @@
         <v>1</v>
       </c>
       <c r="E99">
-        <v>1581.228184359408</v>
+        <v>1581.228184359407</v>
       </c>
       <c r="F99">
-        <v>760.3305785123971</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>761.6222559970973</v>
+        <v>761.6222559970975</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>1705.650794638495</v>
       </c>
       <c r="F101">
-        <v>775.9103641456585</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="B102">
-        <v>591.8499376767587</v>
+        <v>591.8499376767588</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="B103">
-        <v>791.5949524753395</v>
+        <v>791.5949524753396</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="B105">
-        <v>591.8499376767587</v>
+        <v>591.8499376767588</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>1639.424327364622</v>
       </c>
       <c r="F105">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="B107">
-        <v>605.5805846644417</v>
+        <v>605.5805846644415</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>1671.402413673859</v>
       </c>
       <c r="F107">
-        <v>760.330578512397</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4459,10 +4459,10 @@
         <v>1</v>
       </c>
       <c r="E108">
-        <v>1606.505731657477</v>
+        <v>1606.505731657476</v>
       </c>
       <c r="F108">
-        <v>760.3305785123969</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>2148.689637942154</v>
+        <v>2148.689637942153</v>
       </c>
       <c r="F109">
-        <v>760.330578512397</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>1706.311158526236</v>
       </c>
       <c r="F110">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>1643.910778199733</v>
       </c>
       <c r="F111">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="B112">
-        <v>795.9937678155778</v>
+        <v>795.9937678155779</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="B113">
-        <v>615.9968081322153</v>
+        <v>615.9968081322152</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>1706.311158526236</v>
       </c>
       <c r="F113">
-        <v>775.9103641456584</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>1643.910778199733</v>
       </c>
       <c r="F114">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>2204.902736849151</v>
       </c>
       <c r="F115">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="B116">
-        <v>605.8150427085423</v>
+        <v>605.8150427085421</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         <v>1</v>
       </c>
       <c r="E116">
-        <v>1672.049517875577</v>
+        <v>1672.049517875576</v>
       </c>
       <c r="F116">
-        <v>760.3305785123968</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="B118">
-        <v>782.8368460335023</v>
+        <v>782.8368460335022</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>

--- a/Proyecto Interno/interno/03_models/coca/coca_results.xlsx
+++ b/Proyecto Interno/interno/03_models/coca/coca_results.xlsx
@@ -420,7 +420,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>615.5112858433653</v>
+        <v>615.5112858433652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -431,10 +431,10 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1938.860550406601</v>
+        <v>1938.8605504066</v>
       </c>
       <c r="F2">
-        <v>882.3529411764708</v>
+        <v>882.3529411764705</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>610.1280078255213</v>
+        <v>610.1280078255212</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -469,10 +469,10 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1921.903224650393</v>
+        <v>1921.903224650392</v>
       </c>
       <c r="F3">
-        <v>882.3529411764709</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>817.0722755731049</v>
+        <v>818.1970626236806</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -507,10 +507,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2573.777668055281</v>
+        <v>2577.320747264594</v>
       </c>
       <c r="F4">
-        <v>882.3529411764709</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>610.1280078255212</v>
+        <v>610.1280078255213</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>1921.903224650392</v>
       </c>
       <c r="F6">
-        <v>882.3529411764706</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>817.0722755731049</v>
+        <v>818.1970626236806</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2573.777668055281</v>
+        <v>2577.320747264594</v>
       </c>
       <c r="F7">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>1938.860550406601</v>
       </c>
       <c r="F8">
-        <v>882.3529411764706</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>1921.903224650392</v>
       </c>
       <c r="F9">
-        <v>882.3529411764706</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>817.0722755731047</v>
+        <v>818.1970626236806</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -735,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>2573.77766805528</v>
+        <v>2577.320747264595</v>
       </c>
       <c r="F10">
-        <v>882.3529411764705</v>
+        <v>882.3529411764708</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>1705.248306235797</v>
       </c>
       <c r="F11">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>594.7921732203171</v>
+        <v>594.7921732203172</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>2219.870564462949</v>
       </c>
       <c r="F13">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>615.6131069443312</v>
+        <v>615.613106944331</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>1705.248306235797</v>
       </c>
       <c r="F14">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>594.7921732203171</v>
+        <v>594.792173220317</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>1647.574319820278</v>
       </c>
       <c r="F15">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>801.3973156905955</v>
+        <v>801.3973156905953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>2219.870564462949</v>
       </c>
       <c r="F16">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>1614.49207745852</v>
       </c>
       <c r="F18">
-        <v>760.3305785123968</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>788.1510790676106</v>
+        <v>788.1510790676105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>1704.021280462056</v>
       </c>
       <c r="F20">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>596.8116493338342</v>
+        <v>596.8116493338341</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>1653.168268654721</v>
       </c>
       <c r="F21">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>804.2683015495813</v>
+        <v>804.6241424658284</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>2227.82319529234</v>
+        <v>2228.808874630345</v>
       </c>
       <c r="F22">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>615.1701373509227</v>
+        <v>615.1701373509226</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>1704.021280462056</v>
       </c>
       <c r="F23">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>596.8116493338342</v>
+        <v>596.811649333834</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>1653.168268654721</v>
+        <v>1653.16826865472</v>
       </c>
       <c r="F24">
-        <v>775.9103641456584</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>804.2683015495813</v>
+        <v>804.6241424658282</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>2227.82319529234</v>
+        <v>2228.808874630344</v>
       </c>
       <c r="F25">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>1669.805619103612</v>
       </c>
       <c r="F26">
-        <v>760.3305785123968</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>1619.973703365326</v>
       </c>
       <c r="F27">
-        <v>760.3305785123968</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>790.9746106148775</v>
+        <v>791.3245698630874</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2183.089925297062</v>
+        <v>2184.055812822121</v>
       </c>
       <c r="F28">
-        <v>760.3305785123969</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>1708.803270923763</v>
       </c>
       <c r="F29">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>603.9331682446307</v>
+        <v>603.9331682446305</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>1672.894876037627</v>
+        <v>1672.894876037626</v>
       </c>
       <c r="F30">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>815.3976236620928</v>
+        <v>815.3976236620925</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>2258.651417543997</v>
       </c>
       <c r="F31">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>616.8964876981092</v>
+        <v>616.8964876981094</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>1708.803270923763</v>
       </c>
       <c r="F32">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>603.9331682446306</v>
+        <v>603.9331682446307</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>1672.894876037627</v>
       </c>
       <c r="F33">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>1674.491590244355</v>
       </c>
       <c r="F35">
-        <v>760.3305785123968</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>801.9199769899918</v>
+        <v>801.9199769899921</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>2213.299136492377</v>
+        <v>2213.299136492378</v>
       </c>
       <c r="F37">
-        <v>760.3305785123965</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F38">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>1926.316471798963</v>
       </c>
       <c r="F39">
-        <v>882.3529411764707</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>772.0347671759838</v>
+        <v>772.0347671759837</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>2431.909516604349</v>
       </c>
       <c r="F40">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F41">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>2431.909516604349</v>
       </c>
       <c r="F43">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>1940.54280008508</v>
       </c>
       <c r="F44">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>2431.909516604349</v>
       </c>
       <c r="F46">
-        <v>882.3529411764708</v>
+        <v>882.3529411764706</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B47">
-        <v>622.6067439330452</v>
+        <v>615.6307580066247</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2141,10 +2141,10 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>2042.150120100388</v>
+        <v>1705.29719967835</v>
       </c>
       <c r="F47">
-        <v>929.1784702549575</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2164,11 +2164,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B48">
-        <v>603.5743875699116</v>
+        <v>596.8116493338341</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2179,10 +2179,10 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>1979.72399122931</v>
+        <v>1653.168268654721</v>
       </c>
       <c r="F48">
-        <v>929.1784702549575</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2202,11 +2202,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B49">
-        <v>813.3818233801713</v>
+        <v>804.6241424658284</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2217,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>2667.892380686962</v>
+        <v>2228.808874630345</v>
       </c>
       <c r="F49">
-        <v>929.1784702549575</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2240,11 +2240,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B50">
-        <v>622.6067439330452</v>
+        <v>615.6307580066247</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>1</v>
       </c>
       <c r="E50">
-        <v>2042.150120100389</v>
+        <v>1705.29719967835</v>
       </c>
       <c r="F50">
-        <v>929.1784702549576</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2278,11 +2278,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B51">
-        <v>603.5743875699116</v>
+        <v>596.8116493338342</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="E51">
-        <v>1979.72399122931</v>
+        <v>1653.168268654721</v>
       </c>
       <c r="F51">
-        <v>929.1784702549577</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2316,11 +2316,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B52">
-        <v>813.3818233801713</v>
+        <v>804.6241424658284</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>2667.892380686962</v>
+        <v>2228.808874630345</v>
       </c>
       <c r="F52">
-        <v>929.1784702549576</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2354,11 +2354,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco cáscara</t>
         </is>
       </c>
       <c r="B53">
-        <v>622.6067439330452</v>
+        <v>605.4550429982506</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>2042.150120100389</v>
+        <v>1671.055918675172</v>
       </c>
       <c r="F53">
-        <v>929.1784702549576</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2392,11 +2392,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco cáscara</t>
         </is>
       </c>
       <c r="B54">
-        <v>603.5743875699116</v>
+        <v>586.9469939729443</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>1</v>
       </c>
       <c r="E54">
-        <v>1979.72399122931</v>
+        <v>1619.973703365326</v>
       </c>
       <c r="F54">
-        <v>929.1784702549577</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2430,11 +2430,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco cáscara</t>
         </is>
       </c>
       <c r="B55">
-        <v>813.3818233801713</v>
+        <v>791.3245698630874</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>2667.892380686962</v>
+        <v>2184.055812822121</v>
       </c>
       <c r="F55">
-        <v>929.1784702549576</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>593.5728658088276</v>
+        <v>593.6738291541036</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         <v>1</v>
       </c>
       <c r="E57">
-        <v>1644.196838290452</v>
+        <v>1644.476506756867</v>
       </c>
       <c r="F57">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B58">
-        <v>796.4613521440849</v>
+        <v>796.856189960668</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2559,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>2206.197945439115</v>
+        <v>2207.29164619105</v>
       </c>
       <c r="F58">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>616.8938163500694</v>
+        <v>616.8938163500696</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>1708.795871289692</v>
+        <v>1708.795871289693</v>
       </c>
       <c r="F59">
-        <v>775.910364145658</v>
+        <v>775.9103641456585</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="B60">
-        <v>593.5728658088276</v>
+        <v>593.6738291541037</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="E60">
-        <v>1644.196838290452</v>
+        <v>1644.476506756867</v>
       </c>
       <c r="F60">
-        <v>775.9103641456581</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>796.4613521440849</v>
+        <v>796.8561899606681</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>2206.197945439115</v>
+        <v>2207.29164619105</v>
       </c>
       <c r="F61">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>1674.484339190222</v>
       </c>
       <c r="F62">
-        <v>760.330578512397</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>583.7617440599213</v>
+        <v>583.861038589573</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="E63">
-        <v>1611.182413605383</v>
+        <v>1611.456466507221</v>
       </c>
       <c r="F63">
-        <v>760.330578512397</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>783.2967016954223</v>
+        <v>783.6850132671034</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>2161.898896679366</v>
+        <v>2162.970636617205</v>
       </c>
       <c r="F64">
         <v>760.3305785123969</v>
@@ -2810,11 +2810,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B65">
-        <v>580.0376974665129</v>
+        <v>617.4070729335432</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="E65">
-        <v>1711.111207526213</v>
+        <v>1710.217592025914</v>
       </c>
       <c r="F65">
-        <v>776.3157894736839</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2848,11 +2848,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B66">
-        <v>556.027441448955</v>
+        <v>591.8499376767588</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <v>1640.280952274417</v>
+        <v>1639.424327364622</v>
       </c>
       <c r="F66">
-        <v>776.315789473684</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2886,11 +2886,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B67">
-        <v>743.6826264044637</v>
+        <v>791.6409828519764</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>2193.863747893167</v>
+        <v>2192.845522499974</v>
       </c>
       <c r="F67">
-        <v>776.3157894736839</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2924,11 +2924,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B68">
-        <v>624.4031870744332</v>
+        <v>617.4070729335432</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
         <v>1</v>
       </c>
       <c r="E68">
-        <v>2048.042453604141</v>
+        <v>1710.217592025914</v>
       </c>
       <c r="F68">
-        <v>929.1784702549573</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2962,11 +2962,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B69">
-        <v>598.556452551283</v>
+        <v>591.8499376767587</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1963.265164368208</v>
+        <v>1639.424327364622</v>
       </c>
       <c r="F69">
-        <v>929.1784702549575</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3000,11 +3000,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Arroz de segunda</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B70">
-        <v>800.5648669509807</v>
+        <v>791.6409828519766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>2625.852763599216</v>
+        <v>2192.845522499975</v>
       </c>
       <c r="F70">
-        <v>929.1784702549573</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="B71">
-        <v>607.2019973478647</v>
+        <v>607.201997347865</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>1675.877512680107</v>
       </c>
       <c r="F71">
-        <v>760.3305785123966</v>
+        <v>760.330578512397</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>1606.505731657476</v>
+        <v>1606.505731657477</v>
       </c>
       <c r="F72">
-        <v>760.3305785123968</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B73">
-        <v>778.5107383848381</v>
+        <v>778.5560079288034</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3129,10 +3129,10 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>2148.689637942153</v>
+        <v>2148.814581883497</v>
       </c>
       <c r="F73">
-        <v>760.3305785123969</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="B75">
-        <v>595.4824100601712</v>
+        <v>595.6704937585603</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3205,10 +3205,10 @@
         <v>1</v>
       </c>
       <c r="E75">
-        <v>1649.486275866674</v>
+        <v>1650.007267711212</v>
       </c>
       <c r="F75">
-        <v>775.9103641456584</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="B76">
-        <v>753.6439489665659</v>
+        <v>753.6439489665657</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>2087.593738637388</v>
+        <v>2087.593738637387</v>
       </c>
       <c r="F76">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>1707.661220992462</v>
       </c>
       <c r="F77">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>595.4824100601712</v>
+        <v>595.6704937585603</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>1649.486275866674</v>
+        <v>1650.007267711212</v>
       </c>
       <c r="F78">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>753.643948966566</v>
+        <v>753.6439489665659</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <v>1673.372471947861</v>
+        <v>1673.37247194786</v>
       </c>
       <c r="F80">
-        <v>760.3305785123971</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="B81">
-        <v>585.6397255963667</v>
+        <v>585.8247004732949</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -3433,10 +3433,10 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>1616.365642645972</v>
+        <v>1616.876173306294</v>
       </c>
       <c r="F81">
-        <v>760.330578512397</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>2045.676186765115</v>
       </c>
       <c r="F82">
-        <v>760.330578512397</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B83">
-        <v>615.2424032070854</v>
+        <v>615.2424032070855</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>1938.013570102319</v>
       </c>
       <c r="F83">
-        <v>882.3529411764706</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="B84">
-        <v>640.8797137303673</v>
+        <v>641.0918539008137</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>1</v>
       </c>
       <c r="E84">
-        <v>2018.771098250657</v>
+        <v>2019.439339787563</v>
       </c>
       <c r="F84">
         <v>882.3529411764706</v>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="B85">
-        <v>801.1695975506458</v>
+        <v>801.431630700243</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>2523.684232284534</v>
+        <v>2524.509636705765</v>
       </c>
       <c r="F85">
         <v>882.3529411764707</v>
@@ -3608,11 +3608,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B86">
-        <v>578.0040472234987</v>
+        <v>615.2424032070855</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3623,10 +3623,10 @@
         <v>1</v>
       </c>
       <c r="E86">
-        <v>1895.853274893075</v>
+        <v>1938.013570102319</v>
       </c>
       <c r="F86">
-        <v>863.157894736842</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3646,11 +3646,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B87">
-        <v>602.0896257940556</v>
+        <v>641.0918539008137</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
         <v>1</v>
       </c>
       <c r="E87">
-        <v>1974.853972604502</v>
+        <v>2019.439339787563</v>
       </c>
       <c r="F87">
-        <v>863.157894736842</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3684,11 +3684,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Harina precocida de maíz</t>
+          <t>Maíz blanco trillado</t>
         </is>
       </c>
       <c r="B88">
-        <v>752.6777534883697</v>
+        <v>801.431630700243</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3699,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>2468.783031441852</v>
+        <v>2524.509636705765</v>
       </c>
       <c r="F88">
-        <v>863.157894736842</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="B89">
-        <v>615.2424032070854</v>
+        <v>615.2424032070855</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="B90">
-        <v>640.8797137303673</v>
+        <v>641.0918539008137</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>1</v>
       </c>
       <c r="E90">
-        <v>2018.771098250657</v>
+        <v>2019.439339787563</v>
       </c>
       <c r="F90">
         <v>882.3529411764707</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="B91">
-        <v>801.1695975506458</v>
+        <v>801.431630700243</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>2523.684232284535</v>
+        <v>2524.509636705765</v>
       </c>
       <c r="F91">
-        <v>882.3529411764709</v>
+        <v>882.3529411764707</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>1710.237174595826</v>
       </c>
       <c r="F92">
-        <v>775.9103641456581</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="B93">
-        <v>582.5374811456834</v>
+        <v>582.568471080514</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>1</v>
       </c>
       <c r="E93">
-        <v>1613.628822773543</v>
+        <v>1613.714664893024</v>
       </c>
       <c r="F93">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="B94">
-        <v>774.4226300474685</v>
+        <v>774.7826439545263</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>2145.150685231488</v>
+        <v>2146.147923754038</v>
       </c>
       <c r="F94">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1710.237174595826</v>
       </c>
       <c r="F95">
-        <v>775.9103641456581</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="B96">
-        <v>582.5374811456834</v>
+        <v>582.568471080514</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4003,10 +4003,10 @@
         <v>1</v>
       </c>
       <c r="E96">
-        <v>1613.628822773543</v>
+        <v>1613.714664893024</v>
       </c>
       <c r="F96">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="B97">
-        <v>774.4226300474685</v>
+        <v>774.7826439545263</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>2145.150685231488</v>
+        <v>2146.147923754038</v>
       </c>
       <c r="F97">
-        <v>775.9103641456581</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="B99">
-        <v>572.9087624490606</v>
+        <v>572.9392401535633</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4117,10 +4117,10 @@
         <v>1</v>
       </c>
       <c r="E99">
-        <v>1581.228184359407</v>
+        <v>1581.312302823835</v>
       </c>
       <c r="F99">
-        <v>760.3305785123969</v>
+        <v>760.3305785123966</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>761.6222559970975</v>
+        <v>761.9763192610632</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>2102.077426551989</v>
+        <v>2103.054641160534</v>
       </c>
       <c r="F100">
-        <v>760.330578512397</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="B103">
-        <v>791.5949524753396</v>
+        <v>791.6409828519766</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>2192.718018356691</v>
+        <v>2192.845522499975</v>
       </c>
       <c r="F103">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="B104">
-        <v>615.7584096167852</v>
+        <v>615.7584096167851</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>1705.650794638495</v>
       </c>
       <c r="F104">
-        <v>775.9103641456583</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="B105">
-        <v>591.8499376767588</v>
+        <v>591.8499376767587</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>1639.424327364622</v>
       </c>
       <c r="F105">
-        <v>775.9103641456584</v>
+        <v>775.9103641456581</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>791.5949524753396</v>
+        <v>791.6409828519763</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>2192.718018356691</v>
+        <v>2192.845522499974</v>
       </c>
       <c r="F106">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="B107">
-        <v>605.5805846644415</v>
+        <v>605.5805846644417</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>1671.402413673859</v>
       </c>
       <c r="F107">
-        <v>760.3305785123966</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4459,10 +4459,10 @@
         <v>1</v>
       </c>
       <c r="E108">
-        <v>1606.505731657476</v>
+        <v>1606.505731657477</v>
       </c>
       <c r="F108">
-        <v>760.3305785123968</v>
+        <v>760.3305785123969</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="B109">
-        <v>778.5107383848381</v>
+        <v>778.5560079288033</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>2148.689637942153</v>
+        <v>2148.814581883497</v>
       </c>
       <c r="F109">
-        <v>760.3305785123969</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="B111">
-        <v>593.4695950179541</v>
+        <v>593.4848694406776</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>1</v>
       </c>
       <c r="E111">
-        <v>1643.910778199733</v>
+        <v>1643.953088350677</v>
       </c>
       <c r="F111">
         <v>775.9103641456581</v>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="B112">
-        <v>795.9937678155779</v>
+        <v>795.9937678155778</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>2204.902736849151</v>
+        <v>2204.90273684915</v>
       </c>
       <c r="F112">
-        <v>775.9103641456583</v>
+        <v>775.910364145658</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>1706.311158526236</v>
       </c>
       <c r="F113">
-        <v>775.910364145658</v>
+        <v>775.9103641456583</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="B114">
-        <v>593.4695950179541</v>
+        <v>593.4848694406776</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         <v>1</v>
       </c>
       <c r="E114">
-        <v>1643.910778199733</v>
+        <v>1643.953088350677</v>
       </c>
       <c r="F114">
-        <v>775.9103641456581</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>2204.902736849151</v>
       </c>
       <c r="F115">
-        <v>775.9103641456583</v>
+        <v>775.9103641456584</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="B116">
-        <v>605.8150427085421</v>
+        <v>605.8150427085423</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
         <v>1</v>
       </c>
       <c r="E116">
-        <v>1672.049517875576</v>
+        <v>1672.049517875577</v>
       </c>
       <c r="F116">
-        <v>760.3305785123966</v>
+        <v>760.3305785123968</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="B117">
-        <v>583.6601802242689</v>
+        <v>583.6752021771953</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="E117">
-        <v>1610.902097418982</v>
+        <v>1610.943558009059</v>
       </c>
       <c r="F117">
         <v>760.3305785123968</v>
